--- a/artfynd/A 1855-2025 artfynd.xlsx
+++ b/artfynd/A 1855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67043761</v>
+        <v>67043788</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>886641.3505294642</v>
+        <v>886616</v>
       </c>
       <c r="R2" t="n">
-        <v>7341603.159855546</v>
+        <v>7341671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,19 +749,9 @@
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67043898</v>
+        <v>67043890</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,25 +790,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886515.4842682406</v>
+        <v>886515</v>
       </c>
       <c r="R3" t="n">
-        <v>7341656.875851285</v>
+        <v>7341657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +853,9 @@
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67043771</v>
+        <v>67043898</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>886512.6279752954</v>
+        <v>886515</v>
       </c>
       <c r="R4" t="n">
-        <v>7341710.930394101</v>
+        <v>7341657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,32 +953,18 @@
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,61 +983,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67043932</v>
+        <v>67044009</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torrberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>886664.6489086517</v>
+        <v>886760</v>
       </c>
       <c r="R5" t="n">
-        <v>7341629.03624473</v>
+        <v>7341648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,24 +1058,14 @@
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackmärken på gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,45 +1092,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67043890</v>
+        <v>67043771</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886515.4842682406</v>
+        <v>886513</v>
       </c>
       <c r="R6" t="n">
-        <v>7341656.875851285</v>
+        <v>7341711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,19 +1162,14 @@
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-07-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1178,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1272,6 +1193,219 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67043932</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Torrberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>886665</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7341629</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karl Gustav</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67043982</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torrberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>886760</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7341648</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karl Gustav</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1855-2025 artfynd.xlsx
+++ b/artfynd/A 1855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67044009</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043771</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043932</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,8 +1441,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67043982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>